--- a/Airlines-Services/airlines/management/commands/AirlineRoutesWayPoints/WayPoints.xlsx
+++ b/Airlines-Services/airlines/management/commands/AirlineRoutesWayPoints/WayPoints.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WayPoints" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WayPoints" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,36 +413,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F456"/>
+  <dimension ref="A1:F469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>WayPoint</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>WayPoint</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
@@ -12926,12 +12914,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>N37°00\'48.99"</t>
+          <t>N37°00'48.99"</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>W007°58\'30.00"</t>
+          <t>W007°58'30.00"</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -12958,12 +12946,12 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>N37°07\'43.99"</t>
+          <t>N37°07'43.99"</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>W007°22\'59.99"</t>
+          <t>W007°22'59.99"</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
@@ -12990,12 +12978,12 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>N37°09\'54.99"</t>
+          <t>N37°09'54.99"</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>W007°11\'30.99"</t>
+          <t>W007°11'30.99"</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -13022,12 +13010,12 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>N37°57\'00.00"</t>
+          <t>N37°57'00.00"</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>W006°00\'00.00"</t>
+          <t>W006°00'00.00"</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
@@ -13054,12 +13042,12 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>N38°35\'49.99"</t>
+          <t>N38°35'49.99"</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>W005°28\'36.99"</t>
+          <t>W005°28'36.99"</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -13086,12 +13074,12 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>N39°00\'00.00"</t>
+          <t>N39°00'00.00"</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>W005°09\'00.00"</t>
+          <t>W005°09'00.00"</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
@@ -13118,12 +13106,12 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>N39°58\'09.99"</t>
+          <t>N39°58'09.99"</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>W004°20\'15.00"</t>
+          <t>W004°20'15.00"</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
@@ -13150,12 +13138,12 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>N41°09\'05.99"</t>
+          <t>N41°09'05.99"</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>W003°36\'16.99"</t>
+          <t>W003°36'16.99"</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
@@ -13182,12 +13170,12 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>N41°30\'15.00"</t>
+          <t>N41°30'15.00"</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>W003°24\'41.99"</t>
+          <t>W003°24'41.99"</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
@@ -13214,12 +13202,12 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>N42°27\'11.99"</t>
+          <t>N42°27'11.99"</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>W002°52\'51.00"</t>
+          <t>W002°52'51.00"</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
@@ -13246,12 +13234,12 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>N43°38\'47.00"</t>
+          <t>N43°38'47.00"</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>W001°57\'44.99"</t>
+          <t>W001°57'44.99"</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
@@ -13278,12 +13266,12 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>N45°02\'39.99"</t>
+          <t>N45°02'39.99"</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>W001°02\'22.99"</t>
+          <t>W001°02'22.99"</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
@@ -13310,12 +13298,12 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>N45°11\'44.99"</t>
+          <t>N45°11'44.99"</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>W000°51\'42.00"</t>
+          <t>W000°51'42.00"</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
@@ -13342,12 +13330,12 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>N46°34\'52.00"</t>
+          <t>N46°34'52.00"</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>E000°17\'52.99"</t>
+          <t>E000°17'52.99"</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
@@ -13374,12 +13362,12 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>N47°02\'48.99"</t>
+          <t>N47°02'48.99"</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>E000°41\'30.00"</t>
+          <t>E000°41'30.00"</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
@@ -13406,12 +13394,12 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>N47°29\'43.99"</t>
+          <t>N47°29'43.99"</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>E000°44\'18.99"</t>
+          <t>E000°44'18.99"</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
@@ -13438,12 +13426,12 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>N47°50\'14.00"</t>
+          <t>N47°50'14.00"</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>E000°54\'26.00"</t>
+          <t>E000°54'26.00"</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
@@ -13470,12 +13458,12 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>N48°12\'54.00"</t>
+          <t>N48°12'54.00"</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>E001°05\'55.99"</t>
+          <t>E001°05'55.99"</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -13502,12 +13490,12 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>N48°33\'01.99"</t>
+          <t>N48°33'01.99"</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>E001°16\'14.99"</t>
+          <t>E001°16'14.99"</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
@@ -13534,12 +13522,12 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>N48°58\'30.99"</t>
+          <t>N48°58'30.99"</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>E001°29\'10.00"</t>
+          <t>E001°29'10.00"</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
@@ -13566,12 +13554,12 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>N49°21\'03.00"</t>
+          <t>N49°21'03.00"</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>E002°08\'03.00"</t>
+          <t>E002°08'03.00"</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
@@ -13598,12 +13586,12 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>N49°30\'50.99"</t>
+          <t>N49°30'50.99"</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>E002°25\'17.00"</t>
+          <t>E002°25'17.00"</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -13630,12 +13618,12 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>N49°33\'09.99"</t>
+          <t>N49°33'09.99"</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>E002°29\'22.00"</t>
+          <t>E002°29'22.00"</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
@@ -13662,12 +13650,12 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>N49°49\'33.99"</t>
+          <t>N49°49'33.99"</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>E002°45\'18.99"</t>
+          <t>E002°45'18.99"</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
@@ -13694,12 +13682,12 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>N49°54\'45.00"</t>
+          <t>N49°54'45.00"</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>E002°50\'23.99"</t>
+          <t>E002°50'23.99"</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -13726,12 +13714,12 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>N50°00\'00.00"</t>
+          <t>N50°00'00.00"</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>E002°55\'31.99"</t>
+          <t>E002°55'31.99"</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -13758,12 +13746,12 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>N50°13\'41.00"</t>
+          <t>N50°13'41.00"</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>E003°09\'05.00"</t>
+          <t>E003°09'05.00"</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -13790,12 +13778,12 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>N50°24\'14.99"</t>
+          <t>N50°24'14.99"</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>E003°16\'29.99"</t>
+          <t>E003°16'29.99"</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
@@ -13822,12 +13810,12 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>N50°32\'45.00"</t>
+          <t>N50°32'45.00"</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>E003°29\'48.99"</t>
+          <t>E003°29'48.99"</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -15015,6 +15003,422 @@
         </is>
       </c>
       <c r="F456" t="inlineStr">
+        <is>
+          <t>Unknown Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>PISIP</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>WayPoint</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>N41°31'48.99"</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>E016°38'10.99"</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Unknown Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>VIESTE</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>WayPoint</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>N41°54'45.99"</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>E016°02'57.00"</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Unknown Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>ETRIN</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>WayPoint</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>N42°36'21.00"</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>E014°43'12.00"</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Unknown Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>ERLIT</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>WayPoint</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>N43°23'00.99"</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>E013°10'01.99"</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Unknown Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>OGAPU</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>WayPoint</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>N44°09'29.99"</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>E011°33'13.99"</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Unknown Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>IVLOX</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>WayPoint</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>N44°43'09.99"</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>E010°23'12.99"</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Unknown Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>NELAB</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>WayPoint</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>N45°37'41.99"</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>E008°24'23.99"</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Unknown Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>CERVI</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>WayPoint</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>N45°58'12.00"</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>E007°32'42.99"</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Unknown Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>SAPRE</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>WayPoint</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>N46°28'06.99"</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>E006°26'52.99"</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Unknown Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>DINOX</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>WayPoint</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>N46°39'59.99"</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>E006°07'11.00"</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Unknown Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>SIROD</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>WayPoint</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>N46°43'36.99"</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>E006°01'10.00"</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Unknown Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>LISMO</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>WayPoint</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>N46°52'13.99"</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>E005°46'41.00"</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Unknown Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>DIJON</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>WayPoint</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>N47°16'15.00"</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>E005°05'50.00"</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
         <is>
           <t>Unknown Name</t>
         </is>
